--- a/APS-Modules/aps-cx/src/main/resources/excelModel/cxyl.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/cxyl.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-cx\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE22A291-FCD8-467E-B736-2DF7100360A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E63AE31-772A-4B13-9D38-EACA4D5F6D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="成型余量-按机台" sheetId="2" r:id="rId1"/>
@@ -51,44 +51,45 @@
 còn thiếu</t>
   </si>
   <si>
+    <t>胎胚描述
+Mô tả phôi</t>
+  </si>
+  <si>
+    <t>*物料编码
+Mã vật liệu</t>
+  </si>
+  <si>
+    <t>*机台
+Máy</t>
+  </si>
+  <si>
+    <t>{.cxMachineCode}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.mainMaterialDesc}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.smallGlue}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.cxRemainQty}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.remark}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>小胶种 
 Loại 
 su nhỏ</t>
-  </si>
-  <si>
-    <t>胎胚描述
-Mô tả phôi</t>
-  </si>
-  <si>
-    <t>*物料编码
-Mã vật liệu</t>
-  </si>
-  <si>
-    <t>*机台
-Máy</t>
-  </si>
-  <si>
-    <t>{.cxMachineCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.materialCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.mainMaterialDesc}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.smallGlue}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.cxRemainQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.remark}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.embryoCode}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -96,7 +97,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,18 +135,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color theme="0"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -198,9 +206,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -208,22 +219,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{5F53B5CC-20BD-41D1-A474-9CE27526DE68}"/>
+    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -528,52 +540,52 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="66.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="66.33203125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/APS-Modules/aps-cx/src/main/resources/excelModel/cxyl.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/cxyl.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-cx\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E63AE31-772A-4B13-9D38-EACA4D5F6D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F845ADE8-4EF0-4E6A-B6D5-8629A3BB2108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="成型余量-按机台" sheetId="2" r:id="rId1"/>
+    <sheet name="成型余量-按机台" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成型余量-按机台'!$A$1:$F$1</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,34 +62,58 @@
 Máy</t>
   </si>
   <si>
+    <r>
+      <t>TD胶种 
+Lo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i 
+su nh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ỏ</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>{.cxMachineCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.embryoCode}</t>
   </si>
   <si>
     <t>{.mainMaterialDesc}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.smallGlue}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.cxRemainQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.remark}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>小胶种 
-Loại 
-su nhỏ</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.embryoCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -119,12 +142,6 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,13 +152,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -153,6 +163,20 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -209,56 +233,32 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{5F53B5CC-20BD-41D1-A474-9CE27526DE68}"/>
-    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
+    <cellStyle name="千位分隔 2" xfId="2" xr:uid="{4BA4E33C-0390-466A-AF69-19E34552D5CC}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -533,72 +533,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FB0390-D6AA-4DB0-A177-7B342D6E0780}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70EA9289-95B5-401A-ABA1-6A69B65D3FBE}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="66.33203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.6640625" style="1"/>
+    <col min="3" max="3" width="41.109375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="66.33203125" style="2" customWidth="1"/>
+    <col min="7" max="147" width="10.77734375" style="2" customWidth="1"/>
+    <col min="148" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C65490 F3:F65490">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>AND(COUNTIF($C$2:$C$65490, C3)+COUNTIF($F$2:$F$65490, C3)&gt;1,NOT(ISBLANK(C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C65490">
-    <cfRule type="duplicateValues" dxfId="0" priority="5" stopIfTrue="1"/>
-  </conditionalFormatting>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>